--- a/data/trans_orig/IP08-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP08-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15447</t>
+          <t>14749</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>17454</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14879</t>
+          <t>15645</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29139</t>
+          <t>30004</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88905</t>
+          <t>89603</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98552</t>
+          <t>98821</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80669</t>
+          <t>80091</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90804</t>
+          <t>90342</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172759</t>
+          <t>171894</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>187019</t>
+          <t>186253</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,25%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13653</t>
+          <t>13601</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>4998</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13835</t>
+          <t>14127</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11114</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23703</t>
+          <t>23289</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73736</t>
+          <t>73788</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83440</t>
+          <t>83029</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72135</t>
+          <t>71843</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80833</t>
+          <t>80972</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>149656</t>
+          <t>150070</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>162245</t>
+          <t>162298</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,62%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7935</t>
+          <t>7905</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>8590</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20625</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12140</t>
+          <t>11785</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25316</t>
+          <t>25758</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59457</t>
+          <t>59487</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65748</t>
+          <t>66042</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78707</t>
+          <t>79851</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90664</t>
+          <t>90742</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141408</t>
+          <t>140966</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>154584</t>
+          <t>154939</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,93%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>11742</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25233</t>
+          <t>24187</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13962</t>
+          <t>13951</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28130</t>
+          <t>27509</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28539</t>
+          <t>28617</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47753</t>
+          <t>47927</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>175500</t>
+          <t>176546</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>188882</t>
+          <t>188991</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>173944</t>
+          <t>174565</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>188112</t>
+          <t>188123</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>355054</t>
+          <t>354880</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>374268</t>
+          <t>374190</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,9%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4786</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14155</t>
+          <t>14449</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10616</t>
+          <t>10833</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22869</t>
+          <t>23212</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18080</t>
+          <t>18227</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33117</t>
+          <t>33179</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89965</t>
+          <t>89671</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>99334</t>
+          <t>99431</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>104420</t>
+          <t>104077</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>116673</t>
+          <t>116456</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>198293</t>
+          <t>198231</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>213330</t>
+          <t>213183</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,12%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2309</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9786</t>
+          <t>9868</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13282</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20225</t>
+          <t>19969</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>65084</t>
+          <t>65002</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>72561</t>
+          <t>72711</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59110</t>
+          <t>59109</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67862</t>
+          <t>68378</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>127037</t>
+          <t>127293</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>138856</t>
+          <t>139015</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41958</t>
+          <t>42319</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63891</t>
+          <t>65405</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>64880</t>
+          <t>64330</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91946</t>
+          <t>91397</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>113794</t>
+          <t>114608</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>148427</t>
+          <t>148937</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>574965</t>
+          <t>573451</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>596898</t>
+          <t>596537</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>592657</t>
+          <t>593206</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>619723</t>
+          <t>620273</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1175032</t>
+          <t>1174522</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1209665</t>
+          <t>1208851</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11617</t>
+          <t>12152</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>12432</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8904</t>
+          <t>9410</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20508</t>
+          <t>21118</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78316</t>
+          <t>77781</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86670</t>
+          <t>86521</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>76954</t>
+          <t>77331</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85715</t>
+          <t>85787</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>159189</t>
+          <t>158579</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>170793</t>
+          <t>170287</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4662</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>14165</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>13598</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10768</t>
+          <t>11118</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23757</t>
+          <t>24042</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79785</t>
+          <t>79101</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88604</t>
+          <t>88863</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>83359</t>
+          <t>83180</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92172</t>
+          <t>92209</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>166287</t>
+          <t>166002</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>179276</t>
+          <t>178926</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,15%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13511</t>
+          <t>13687</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7557</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18492</t>
+          <t>18214</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>14138</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28246</t>
+          <t>28005</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72646</t>
+          <t>72470</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81960</t>
+          <t>81742</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68398</t>
+          <t>68676</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79333</t>
+          <t>79362</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>144801</t>
+          <t>145042</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>159136</t>
+          <t>158909</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25896</t>
+          <t>26299</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43546</t>
+          <t>43988</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30731</t>
+          <t>29557</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49560</t>
+          <t>49105</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>62334</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87079</t>
+          <t>87211</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>161828</t>
+          <t>161386</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>179478</t>
+          <t>179075</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>178546</t>
+          <t>179001</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>197375</t>
+          <t>198549</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>346400</t>
+          <t>346268</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>372368</t>
+          <t>371145</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,62%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>11697</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24921</t>
+          <t>24033</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16605</t>
+          <t>16755</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31919</t>
+          <t>31091</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31751</t>
+          <t>32556</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52254</t>
+          <t>52407</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124248</t>
+          <t>125136</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>137419</t>
+          <t>137472</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>109138</t>
+          <t>109966</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124452</t>
+          <t>124302</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>237972</t>
+          <t>237819</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>258475</t>
+          <t>257670</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,78%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9422</t>
+          <t>9728</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11575</t>
+          <t>12372</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7318</t>
+          <t>6954</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18126</t>
+          <t>17981</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44489</t>
+          <t>44183</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51734</t>
+          <t>51758</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62463</t>
+          <t>61666</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>70352</t>
+          <t>70392</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>109823</t>
+          <t>109968</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>120631</t>
+          <t>120995</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,56%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66931</t>
+          <t>66518</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94473</t>
+          <t>94477</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>83393</t>
+          <t>82133</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>112919</t>
+          <t>113032</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>158541</t>
+          <t>158483</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>198974</t>
+          <t>198427</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>583337</t>
+          <t>583333</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>610879</t>
+          <t>611292</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>603714</t>
+          <t>603601</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>633240</t>
+          <t>634500</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1195469</t>
+          <t>1196016</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1235902</t>
+          <t>1235960</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10195</t>
+          <t>10546</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13141</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>7857</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19940</t>
+          <t>19366</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72418</t>
+          <t>72067</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80306</t>
+          <t>79857</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85977</t>
+          <t>86772</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94958</t>
+          <t>95076</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>161791</t>
+          <t>162365</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>173532</t>
+          <t>173874</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14140</t>
+          <t>14041</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>6657</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17151</t>
+          <t>17239</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99711</t>
+          <t>99808</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>98606</t>
+          <t>98705</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107828</t>
+          <t>108036</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>201309</t>
+          <t>201221</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>212224</t>
+          <t>211803</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7610</t>
+          <t>7493</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10412</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15328</t>
+          <t>14937</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54230</t>
+          <t>54347</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60652</t>
+          <t>60585</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65016</t>
+          <t>64928</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72888</t>
+          <t>72512</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>121940</t>
+          <t>122331</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>131877</t>
+          <t>131919</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11230</t>
+          <t>11326</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24747</t>
+          <t>24105</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16815</t>
+          <t>16989</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20703</t>
+          <t>20484</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37567</t>
+          <t>37092</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>197929</t>
+          <t>198571</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>211446</t>
+          <t>211350</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>192318</t>
+          <t>192144</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>202654</t>
+          <t>202854</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>394242</t>
+          <t>394717</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>411106</t>
+          <t>411325</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>8951</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19651</t>
+          <t>20851</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5432</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15768</t>
+          <t>15648</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17144</t>
+          <t>16201</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33034</t>
+          <t>32158</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>116543</t>
+          <t>115343</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128050</t>
+          <t>127243</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>126648</t>
+          <t>126768</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>136984</t>
+          <t>137226</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>245576</t>
+          <t>246452</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>261466</t>
+          <t>262409</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,18%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>770</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7381</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12750</t>
+          <t>12762</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16287</t>
+          <t>16035</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52941</t>
+          <t>53685</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59576</t>
+          <t>59552</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55075</t>
+          <t>55063</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>64159</t>
+          <t>64176</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111860</t>
+          <t>112112</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>122466</t>
+          <t>122191</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34795</t>
+          <t>35953</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55623</t>
+          <t>56109</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39466</t>
+          <t>40030</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62714</t>
+          <t>61617</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>79243</t>
+          <t>80399</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>111218</t>
+          <t>109931</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>613736</t>
+          <t>613250</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>634564</t>
+          <t>633406</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>643951</t>
+          <t>645048</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>667199</t>
+          <t>666635</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1264806</t>
+          <t>1266093</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1296781</t>
+          <t>1295625</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,16%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16668</t>
+          <t>15800</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8636</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21590</t>
+          <t>22146</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17468</t>
+          <t>17725</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33256</t>
+          <t>33521</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87794</t>
+          <t>88662</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>97925</t>
+          <t>98470</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>115318</t>
+          <t>114762</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128272</t>
+          <t>128283</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>208114</t>
+          <t>207849</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>223902</t>
+          <t>223645</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,66%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>4485</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13409</t>
+          <t>14077</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18171</t>
+          <t>18873</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12333</t>
+          <t>12964</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26782</t>
+          <t>28217</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81272</t>
+          <t>80604</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90361</t>
+          <t>90196</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>77402</t>
+          <t>76700</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89262</t>
+          <t>88936</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>163472</t>
+          <t>162037</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>177921</t>
+          <t>177290</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>796</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13556</t>
+          <t>13500</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16892</t>
+          <t>16542</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45047</t>
+          <t>45082</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50617</t>
+          <t>50622</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50297</t>
+          <t>50353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59861</t>
+          <t>60143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>98379</t>
+          <t>98729</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>108919</t>
+          <t>109637</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>15907</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44117</t>
+          <t>44987</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23180</t>
+          <t>22768</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42637</t>
+          <t>42617</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42506</t>
+          <t>42477</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76109</t>
+          <t>77772</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>173893</t>
+          <t>173023</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>203264</t>
+          <t>202103</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>175635</t>
+          <t>175655</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>195092</t>
+          <t>195504</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>360173</t>
+          <t>358510</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>393776</t>
+          <t>393805</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7991</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19669</t>
+          <t>19538</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14145</t>
+          <t>13582</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57838</t>
+          <t>57404</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26591</t>
+          <t>26509</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79107</t>
+          <t>75492</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99759</t>
+          <t>99890</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111437</t>
+          <t>111266</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>102791</t>
+          <t>103225</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>146484</t>
+          <t>147047</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>200951</t>
+          <t>204566</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>253467</t>
+          <t>253549</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>8593</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2716</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11102</t>
+          <t>10641</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16402</t>
+          <t>16393</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>59895</t>
+          <t>60302</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67160</t>
+          <t>67327</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60901</t>
+          <t>61362</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69287</t>
+          <t>69342</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>124496</t>
+          <t>124505</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>135213</t>
+          <t>135373</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,08%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50974</t>
+          <t>49815</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>83798</t>
+          <t>83807</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78411</t>
+          <t>78314</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>128649</t>
+          <t>134798</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>133324</t>
+          <t>136142</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>199520</t>
+          <t>202504</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>573096</t>
+          <t>573087</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>605920</t>
+          <t>607079</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>618589</t>
+          <t>612440</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>668827</t>
+          <t>668924</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1204612</t>
+          <t>1201628</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1270808</t>
+          <t>1267990</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,3%</t>
         </is>
       </c>
     </row>
